--- a/www/download/COUNTRY.GRC.rpO2.xlsx
+++ b/www/download/COUNTRY.GRC.rpO2.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>Grécia</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 2</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>0.679458599438868</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>0.706339394472836</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>0.800262461767013</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>0.866003342473462</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>0.897674167783526</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>1.06845595822537</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>1.11656988055068</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>1.05752964521951</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.884017000429297</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>0.803923181967953</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>0.803793922933501</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>0.796432005396897</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>0.729660721270685</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.679902072169601</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>0.716948695892488</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>4.131</t>
+          <t>-0.512269780468871</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>4.115</t>
+          <t>-0.554392383924814</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>4.092</t>
+          <t>-0.399934578563206</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>4.261</t>
+          <t>-0.463668016392494</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>4.262</t>
+          <t>-0.609558331133018</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4.255</t>
+          <t>-0.781880253946279</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4.261</t>
+          <t>-0.814437141483582</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4.356</t>
+          <t>-0.832102962620489</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>4.408</t>
+          <t>-0.851578979251589</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>4.514</t>
+          <t>-0.833140008616432</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>4.551</t>
+          <t>-0.880641111738262</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>4.701</t>
+          <t>-0.89994069675644</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>4.783</t>
+          <t>-0.879467488150038</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>4.947</t>
+          <t>-0.874582777913801</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>5.035</t>
+          <t>-0.818540075262514</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2.406</t>
+          <t>-0.226919926486525</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2.405</t>
+          <t>-0.312130060144666</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2.403</t>
+          <t>-0.0992611318368884</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2.518</t>
+          <t>-0.214986235502093</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2.574</t>
+          <t>-0.444722664555478</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2.595</t>
+          <t>-0.695367861013358</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2.644</t>
+          <t>-0.738521064297143</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2.744</t>
+          <t>-0.761470599871717</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2.797</t>
+          <t>-0.793804615329675</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2.903</t>
+          <t>-0.773328312369011</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2.918</t>
+          <t>-0.841927375657534</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>3.031</t>
+          <t>-0.870050371025399</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>-0.843765851394748</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>-0.832063102428699</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>3.091</t>
+          <t>-0.757201346378086</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>8769.443</t>
+          <t>-0.383692621254965</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8633.201</t>
+          <t>-0.424657898392081</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>8451.014</t>
+          <t>-0.212652039345328</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>8788.894</t>
+          <t>-0.279718253630456</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>8982.557</t>
+          <t>-0.459667291105192</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>9024.035</t>
+          <t>-0.686297961274851</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>9037.172</t>
+          <t>-0.732014067518491</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>9187.541</t>
+          <t>-0.755283302780273</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>9268.693</t>
+          <t>-0.820202696323598</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>9400.019</t>
+          <t>-0.768099304107914</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>9491.005</t>
+          <t>-0.838235694187167</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>10097.279</t>
+          <t>-0.867154955885105</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>10117.274</t>
+          <t>-0.839263201802019</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>10032.667</t>
+          <t>-0.835543198192638</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>10458.883</t>
+          <t>-0.76201515612035</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>5114.592</t>
+          <t>98837368503.9722</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>5050.397</t>
+          <t>116582125299.443</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>4945.373</t>
+          <t>97245909298.6779</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>5210.599</t>
+          <t>101808107745.274</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>5317.495</t>
+          <t>125517145932.276</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>5369.195</t>
+          <t>277534262554.749</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5488.763</t>
+          <t>256077586466.54</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>5677.239</t>
+          <t>227963233717.323</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>5760.728</t>
+          <t>265471633172.916</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>5936.407</t>
+          <t>296648206772.751</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>5983.249</t>
+          <t>371796881895.693</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>6409.294</t>
+          <t>513360221846.308</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>6479.312</t>
+          <t>411795011141.878</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>6512.389</t>
+          <t>418043128851.193</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>6172.579</t>
+          <t>270838732542.706</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>22.53</t>
+          <t>21714361704.6126</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>23.29</t>
+          <t>23676179384.161</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>23.72</t>
+          <t>20064380246.8133</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>24.12</t>
+          <t>23178234624.929</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>23.39</t>
+          <t>31041184391.9394</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>24.08</t>
+          <t>53620801737.1614</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>23.86</t>
+          <t>55288836301.9557</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>24.92</t>
+          <t>60141020370.3839</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>23.26</t>
+          <t>71005342279.4953</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>26.08</t>
+          <t>75300720689.0827</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>25.42</t>
+          <t>86221487792.5292</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>26.32</t>
+          <t>118908547366.182</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>26.78</t>
+          <t>100042546515.007</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>26.9</t>
+          <t>110219013586.523</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>26.97</t>
+          <t>82146973162.7534</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>29.1</t>
+          <t>24213083.6312182</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>30.62</t>
+          <t>26818846.6700252</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>32.83</t>
+          <t>24545222.5481733</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>35.16</t>
+          <t>27743835.9716936</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>38.54</t>
+          <t>32122047.3590423</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>64487354.0318259</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>39.78</t>
+          <t>61617721.6522045</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>40.72</t>
+          <t>48689257.1826631</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>39.55</t>
+          <t>44512452.1075389</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>43.32</t>
+          <t>41907851.1167415</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>44.09</t>
+          <t>47796752.7198437</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>39.91</t>
+          <t>57313226.7628874</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>40.17</t>
+          <t>41465057.4725629</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>40.43</t>
+          <t>35527359.568335</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>40.06</t>
+          <t>27897066.2839462</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>48.37</t>
+          <t>3983.48682549415</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>46.09</t>
+          <t>4126.56819191162</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>43.45</t>
+          <t>4499.5063138812</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>40.72</t>
+          <t>4469.70452151192</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>38.06</t>
+          <t>4014.36291494915</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>35.92</t>
+          <t>3062.57627712541</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>36.36</t>
+          <t>2493.52117191839</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>34.35</t>
+          <t>2629.95485824809</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>37.19</t>
+          <t>2664.844653657</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>30.6</t>
+          <t>3396.01133433825</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>30.49</t>
+          <t>2598.56678318696</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>33.76</t>
+          <t>3185.97613475307</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>33.05</t>
+          <t>3972.75336944352</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>32.67</t>
+          <t>4371.97233863899</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>32.97</t>
+          <t>5176.85836373567</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>17.22</t>
+          <t>41436.3928747192</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>50751.9835473069</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>17.97</t>
+          <t>41701.6927553032</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>18.25</t>
+          <t>42941.843548381</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>17.58</t>
+          <t>49299.7098549978</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>18.01</t>
+          <t>85972.9200288687</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>17.8</t>
+          <t>75452.9849031966</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>18.52</t>
+          <t>70583.4092434796</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>18.84</t>
+          <t>84038.5760835244</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>20.04</t>
+          <t>101435.430314706</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>19.94</t>
+          <t>122894.062175284</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>21.05</t>
+          <t>179829.919884068</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>21.61</t>
+          <t>183839.910785312</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>22.04</t>
+          <t>208829.005659194</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>22.12</t>
+          <t>156255.369321859</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>35.57</t>
+          <t>-0.377326674764476</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>36.32</t>
+          <t>-0.43163944755415</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>37.84</t>
+          <t>-0.238989679412458</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>39.37</t>
+          <t>-0.320804574867693</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>41.65</t>
+          <t>-0.506134674182293</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>42.11</t>
+          <t>-0.723353703407146</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>41.84</t>
+          <t>-0.764088616781327</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>43.03</t>
+          <t>-0.786219183298239</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>44.07</t>
+          <t>-0.821766977985073</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>45.82</t>
+          <t>-0.795549645646338</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>46.32</t>
+          <t>-0.856112123586877</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>41.97</t>
+          <t>-0.88129881528934</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>42.02</t>
+          <t>-0.857157210799548</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>42.98</t>
+          <t>-0.850529754376181</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>42.71</t>
+          <t>-0.784026612986282</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>47.21</t>
+          <t>23188.1171342923</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>45.98</t>
+          <t>25900.4379928804</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>44.18</t>
+          <t>25440.6005235069</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>42.38</t>
+          <t>26326.9602209037</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>40.77</t>
+          <t>28279.773219909</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>39.89</t>
+          <t>26109.0195990388</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>40.36</t>
+          <t>26244.8068278759</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>38.45</t>
+          <t>32235.9102570489</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>37.09</t>
+          <t>40148.5025167437</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>34.14</t>
+          <t>48118.0436104442</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>33.74</t>
+          <t>50696.7558147196</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>36.98</t>
+          <t>52673.3696423062</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>36.38</t>
+          <t>64730.9968994728</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>34.98</t>
+          <t>79534.767314545</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>35.18</t>
+          <t>77802.7010297477</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.679458599438868</t>
+          <t>9023.98155862544</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.706339394472836</t>
+          <t>9843.38238945963</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.800262461767013</t>
+          <t>8348.40457822647</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.866003342473462</t>
+          <t>9205.88785791867</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.897674167783526</t>
+          <t>12061.2693737197</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.06845595822537</t>
+          <t>20662.333782704</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.11656988055068</t>
+          <t>20912.1569938645</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.05752964521951</t>
+          <t>21916.9140642628</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.884017000429297</t>
+          <t>25383.9724356146</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.803923181967953</t>
+          <t>25939.5846637145</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.803793922933501</t>
+          <t>29544.05483015</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.796432005396897</t>
+          <t>39226.2938356737</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.729660721270685</t>
+          <t>32167.1629069086</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.679902072169601</t>
+          <t>35328.6904056276</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.716948695892488</t>
+          <t>26576.0684807063</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>-2977151619.615</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>957012915.146723</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>-4052516432.72468</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>-4658844162.77447</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>-440943213.633322</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>36035235160.5735</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>23868648730.9982</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>7817177090.91658</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>21262757651.6171</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>48785899067.0357</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.085</t>
+          <t>75648815239.6507</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>144409110198.423</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>97374916139.4287</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>101160568289.716</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>77406422405.0414</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>348521696.403782</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>3903201860.87561</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>2127538589.15119</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>2606892803.50655</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>16346633309.3216</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>65025032490.7056</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>74943997581.7452</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>46567530930.6711</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>52232765354.4598</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>82765803552.9686</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>109031800167.234</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.134</t>
+          <t>167355606997.339</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.157</t>
+          <t>136690030914.075</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>146249318332.115</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.178</t>
+          <t>98541947887.9247</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.335</t>
+          <t>-3325673316.01879</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.357</t>
+          <t>-2946188945.72888</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.347</t>
+          <t>-6180055021.87587</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.352</t>
+          <t>-7265736966.28102</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.369</t>
+          <t>-16787576522.9549</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>-28989797330.1321</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.351</t>
+          <t>-51075348850.7469</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.398</t>
+          <t>-38750353839.7545</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.515</t>
+          <t>-30970007702.8428</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.607</t>
+          <t>-33979904485.933</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.647</t>
+          <t>-33382984927.5838</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.704</t>
+          <t>-22946496798.9165</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.825</t>
+          <t>-39315114774.6463</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0.951</t>
+          <t>-45088750042.3988</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0.926</t>
+          <t>-21135525482.8833</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.213</t>
+          <t>5618.99260397335</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.223</t>
+          <t>5594.59025280903</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.214</t>
+          <t>6353.22204447063</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.213</t>
+          <t>6252.59691737941</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.217</t>
+          <t>5956.64272902723</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.202</t>
+          <t>5716.15811995047</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.207</t>
+          <t>4933.41588250862</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.236</t>
+          <t>4685.41578824041</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.303</t>
+          <t>4524.26211794318</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.357</t>
+          <t>5303.35727628326</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.375</t>
+          <t>4251.03131014316</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.408</t>
+          <t>4656.20755010291</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.478</t>
+          <t>4594.84727028814</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.538</t>
+          <t>5280.58803249703</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.489</t>
+          <t>5739.72352328665</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>4659.47222728703</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>4664.96479175034</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>5271.53920749971</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>5228.68556391263</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>5163.45434878524</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.113</t>
+          <t>5011.89217828592</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>4412.65211753019</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>4222.34222346034</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.175</t>
+          <t>4148.03525692342</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.207</t>
+          <t>4895.89093578288</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.217</t>
+          <t>3927.33565710909</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.234</t>
+          <t>4342.84106062438</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.274</t>
+          <t>4265.31533140742</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.308</t>
+          <t>4252.29255511819</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.294</t>
+          <t>4321.69714627191</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-51.23</t>
+          <t>9517.20989534908</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>-55.44</t>
+          <t>9875.90258828941</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>-39.99</t>
+          <t>11243.1593819634</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-46.37</t>
+          <t>11441.1366680779</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-60.96</t>
+          <t>16562.4641008493</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-78.19</t>
+          <t>17852.1576033361</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-81.44</t>
+          <t>19156.7134472966</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-83.21</t>
+          <t>19530.9315061937</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>-85.16</t>
+          <t>25944.0608908084</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-83.31</t>
+          <t>35763.2205205283</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>-88.06</t>
+          <t>36377.8948916852</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>-89.99</t>
+          <t>43164.5002693218</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>-87.95</t>
+          <t>50132.4663304368</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>-87.46</t>
+          <t>58538.3917396594</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>-81.85</t>
+          <t>45928.476626247</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-22.69</t>
+          <t>7309436225.65575</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>-31.21</t>
+          <t>8857741931.81073</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>-9.93</t>
+          <t>8645212963.04613</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-21.5</t>
+          <t>9097556527.39787</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-44.47</t>
+          <t>14768883638.7905</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-69.54</t>
+          <t>41422608205.1983</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-73.85</t>
+          <t>30843137508.9596</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>-76.15</t>
+          <t>26667423032.0118</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>-79.38</t>
+          <t>35855439005.049</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-77.33</t>
+          <t>44529502557.2429</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>-84.19</t>
+          <t>56184177144.9655</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>-87.01</t>
+          <t>87640735041.6436</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>-84.38</t>
+          <t>67606455245.9655</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>-83.21</t>
+          <t>74229256486.0792</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>-75.72</t>
+          <t>41868531863.0308</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-38.37</t>
+          <t>27379.0023591856</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>-42.47</t>
+          <t>29656.0043841906</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>-21.27</t>
+          <t>30845.7243839217</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-27.97</t>
+          <t>32574.0740567476</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-45.97</t>
+          <t>37335.6888861809</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-68.63</t>
+          <t>40427.1249225883</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>-73.2</t>
+          <t>42303.4920150895</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-75.53</t>
+          <t>46533.9206465096</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>-82.02</t>
+          <t>57366.289499536</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-76.81</t>
+          <t>67830.34461642</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>-83.82</t>
+          <t>68675.0827026557</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>-86.72</t>
+          <t>80437.733576592</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>-83.93</t>
+          <t>98724.6647008702</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>-83.55</t>
+          <t>115536.132830554</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>-76.2</t>
+          <t>89996.0692386105</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>19249.3</t>
+          <t>78291220357.8927</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>19195.649</t>
+          <t>88357197410.0979</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>21571.866</t>
+          <t>71914571742.9733</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>22280.595</t>
+          <t>83785827944.0843</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>22006.467</t>
+          <t>116704985289.175</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>21326.158</t>
+          <t>236117121247.395</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>18800.316</t>
+          <t>229065636512.708</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>18394.566</t>
+          <t>229358864097.037</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>18284.627</t>
+          <t>274760969758.661</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>22102.24</t>
+          <t>296967330147.24</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>17871.738</t>
+          <t>347146193427.392</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>20414.936</t>
+          <t>463093665666.007</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>20399.655</t>
+          <t>389166458103.28</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>21034.964</t>
+          <t>405215332734.255</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>21758.846</t>
+          <t>262138113464.792</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>13520.954</t>
+          <t>-17861.7924638365</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>13456.606</t>
+          <t>-19780.1017959012</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>15269.2</t>
+          <t>-19602.5650019583</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>15742.551</t>
+          <t>-21132.9373886698</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>15330.165</t>
+          <t>-20773.2247853316</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>14833.996</t>
+          <t>-22574.9673192522</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>13043.266</t>
+          <t>-23146.7785677929</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>12856.996</t>
+          <t>-27002.9891403158</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>12655.497</t>
+          <t>-31422.2286087276</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>15395.259</t>
+          <t>-32067.1240958916</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>12406.227</t>
+          <t>-32297.1878109705</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>14114.585</t>
+          <t>-37273.2333072702</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>14290.356</t>
+          <t>-48592.1983704333</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>16474.463</t>
+          <t>-56997.7410908951</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>17741.56</t>
+          <t>-44067.5926123636</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>98837.369</t>
+          <t>-70981784132.237</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>116582.125</t>
+          <t>-79499455478.2872</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>97245.909</t>
+          <t>-63269358779.9272</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>101808.108</t>
+          <t>-74688271416.6865</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>125517.146</t>
+          <t>-101936101650.384</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>277534.263</t>
+          <t>-194694513042.196</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>256077.586</t>
+          <t>-198222499003.749</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>227963.234</t>
+          <t>-202691441065.025</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>265471.633</t>
+          <t>-238905530753.612</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>296648.207</t>
+          <t>-252437827589.997</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>371796.882</t>
+          <t>-290962016282.426</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>513360.222</t>
+          <t>-375452930624.363</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>411795.011</t>
+          <t>-321560002857.315</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>418043.129</t>
+          <t>-330986076248.176</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>270838.733</t>
+          <t>-220269581601.761</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>50208.82181</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>51048.6571</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>47709.23426</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>48815.60137</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>50355.49576</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>45772.90765</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>47053.17099</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>50218.51051</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.084</t>
+          <t>67831.47736</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>79997.73572</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>86712.20132</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>92843.80953</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.184</t>
+          <t>109147.8607</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.209</t>
+          <t>121188.13372</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.156</t>
+          <t>112371.99438</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>9501.729</t>
+          <t>0.107710215711266</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>9479.119</t>
+          <t>0.102345594545911</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>10492.586</t>
+          <t>0.097288715639229</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>10596.94</t>
+          <t>0.0920996050398652</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>10220.575</t>
+          <t>0.0764967083446135</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>9886.483</t>
+          <t>0.0752339080694597</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>8462.686</t>
+          <t>0.078198240037305</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>8493.965</t>
+          <t>0.0613470625751352</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>8418.047</t>
+          <t>0.0705451310846372</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>9931.645</t>
+          <t>0.0712013603936523</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>7861.56</t>
+          <t>0.0674462050488443</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>9095.002</t>
+          <t>0.067809663644353</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>8898.829</t>
+          <t>0.0632153662072067</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>8752.007</t>
+          <t>0.0508536906746814</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>8973.092</t>
+          <t>0.0411362156697518</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>42013.1707374524</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>43965.1707252105</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>44094.2960000242</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>44965.6765175738</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>47241.814729578</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>42409.5159224413</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>42875.220364943</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>52357.9240787107</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>67858.6070569255</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>80668.4721738653</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>85337.7830020339</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>92697.5696416739</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>110178.122073115</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>127430.075197121</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>125213.580103711</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>21714.362</t>
+          <t>59812.6542822835</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>23676.179</t>
+          <t>62715.6626402422</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>20064.38</t>
+          <t>62295.0916240648</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>23178.235</t>
+          <t>63640.3871769388</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>31041.184</t>
+          <t>67815.6729060742</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>53620.802</t>
+          <t>60970.220312147</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>55288.836</t>
+          <t>61799.5299179561</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>60141.02</t>
+          <t>74908.7324890371</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>71005.342</t>
+          <t>98041.926950747</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>75300.721</t>
+          <t>115811.88345511</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>86221.488</t>
+          <t>122932.982734002</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>118908.547</t>
+          <t>134075.134062603</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>100042.547</t>
+          <t>157280.592704313</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>110219.014</t>
+          <t>180484.72896841</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>82146.973</t>
+          <t>177848.072136483</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>-37.73</t>
+          <t>335225.885817694</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>-43.16</t>
+          <t>356932.075473853</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>-23.9</t>
+          <t>346539.195742387</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-32.08</t>
+          <t>352321.394300357</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-50.61</t>
+          <t>368559.8096196</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-72.34</t>
+          <t>340139.918760941</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>-76.41</t>
+          <t>351157.720698932</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>-78.62</t>
+          <t>397789.440595074</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>-82.18</t>
+          <t>515373.910056097</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-79.55</t>
+          <t>607139.36665598</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>-85.61</t>
+          <t>646730.500102854</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>-88.13</t>
+          <t>703683.416354248</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>-85.72</t>
+          <t>824697.360216687</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>-85.05</t>
+          <t>950797.044925546</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>-78.4</t>
+          <t>926219.70721984</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>24.213</t>
+          <t>59812.6542822835</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>26.819</t>
+          <t>61487.3810369504</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>24.545</t>
+          <t>64807.0802257089</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>27.744</t>
+          <t>67751.1583199923</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>32.122</t>
+          <t>72282.4949672196</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>64.487</t>
+          <t>74965.8991244227</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>61.618</t>
+          <t>75792.6269642812</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>48.689</t>
+          <t>82742.8481057962</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>44.512</t>
+          <t>86873.6077445838</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>41.908</t>
+          <t>90844.890820531</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>47.797</t>
+          <t>94335.9530956879</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>57.313</t>
+          <t>99751.5252418062</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>41.465</t>
+          <t>103976.826848231</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>35.527</t>
+          <t>110049.14255946</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>27.897</t>
+          <t>113859.387885602</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>42013.1707374524</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>43274.2497793281</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>45783.3205613121</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>47524.1521255572</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>49713.0725772694</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>51407.4949265036</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>51951.26907869</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>56567.0070135727</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>59148.2317585172</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>61118.0189527258</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>63135.5201386857</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>65651.5866472667</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>69587.347001906</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>73141.7950645351</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>75019.8676393409</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>59295.3696077165</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>62430.8634697578</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>59154.9537959352</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>58775.6214830612</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>56473.3854839258</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>51699.0749778529</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>53704.7225620439</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>56639.1239609629</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>76505.6225592531</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>91347.1924648905</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>94316.2737359984</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>100389.905417397</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>116864.542535687</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>127886.30613159</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>115903.874663517</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>13520953807.978</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>13456606394.5888</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>15269200444.0178</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>15742550919.895</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>15330164643.4927</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>14833996220.9253</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>13043265848.5451</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>12856996452.0579</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>12655496733.6787</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>15395259027.9691</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>12406226779.6471</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>14114585444.5893</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>14290356382.9196</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>16474463033.1927</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>17741560026.8848</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>19249300195.3405</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>19195649033.1931</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>21571865909.4994</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>22280595184.7125</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>22006466877.0748</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>21326157538.6384</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>18800316154.039</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>18394566339.0294</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>18284626521.2588</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>22102240147.3722</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>17871737568.5763</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>20414935828.8096</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>20399655390.477</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>21034964050.4406</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>21758846011.4198</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>9501728504.51698</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>9479118969.95528</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>10492585647.6863</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>10596940464.4431</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>10220574873.6209</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>9886483421.80608</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>8462685529.63538</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>8493965089.56815</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>8418046750.99833</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>9931644883.70416</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>7861559869.4152</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>9095001634.81294</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>8898829481.83324</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>8752007365.67338</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>8973091701.56713</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>4131219</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>4114854</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>4092138</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>4261223</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>4261966</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>4255111</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>4260548</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>4356484</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>4408021</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>4514447</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>4550601</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>4700825</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>4782684</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>4946734.91482196</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>5034791.95208993</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2406295</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2405289</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>2403379</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2517762</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2573625</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>2595099</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2643861</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>2744046</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>2797251</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>2902927</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>2918404</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>3031348</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>3110083</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>3119816</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>3091013</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>8769442990</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>8633201448</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>8451013902</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>8788894157</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>8982557105</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>9024035231</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>9037172446</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>9187540591</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>9268692553</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>9400019109</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>9491004683</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>10097278528</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>10117273801</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>10032667395.8805</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>10458882644.303</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>5114592005.43904</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>5050397458.99384</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>4945373426.299</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>5210599326.69538</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>5317495219.36193</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>5369195369</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>5488762918</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>5677239118</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>5760728069</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>5936406620</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>5983249244</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>6409294101</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>6479312411</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>6512388590</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>6172579253</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.225340966083084</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.232948823909172</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.237226927667791</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.24118163639277</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.233904920813957</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.240836708288808</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.238602990085928</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.249243487413833</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.232599008054927</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.260788914447732</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.254222469856819</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.263245722347744</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.26784910933332</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.269016670729613</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.269727118190763</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.290971559363126</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.306187083248416</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.328277512911752</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.351647277091884</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.385448066759675</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.399968076680631</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.39776995231038</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.407244687140934</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.395545170131403</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.433181801876958</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.440875469224604</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.399134350888723</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.401697600956369</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.404309922144322</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.400615216883796</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.483687474553789</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.460864092842412</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.434495559420457</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.407171086515346</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.380647012426368</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.359195215030561</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.363627057603692</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.343511825445232</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.371855821813671</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.30602928367531</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.304902060918577</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.337619926763533</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.330453289710311</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.326673407126065</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.329657664925441</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.172193539866581</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.17704560351668</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.179749176991545</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.182463532496045</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.175757547097627</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.180077572106593</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.178048293074848</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.185226550922153</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.188413467972605</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.200397403569388</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.199401207613155</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.210451308834914</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.216063946478499</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.220359943781744</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.22116539207647</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.355690066285184</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.363197207031498</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.378439299976295</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.393739663077918</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.416540282371946</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.421060563778224</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.418399661683136</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.430252042245956</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.440702665586576</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.458203819898153</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.463184319015617</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.419702690233041</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.420181667462409</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.429839901364051</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.427056382349114</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.472116393848235</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.459757189451821</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.441811523032161</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.423796804426037</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.407702170530427</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.398861864115183</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.403552045242015</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.384521406831891</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.370883866440819</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.341398776532459</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.337414473371228</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.369846000932046</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.363754386059092</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.349800154854205</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.351778225574416</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>213345.15517</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>223447.60162</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>213900.888</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>213400.04529</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>217235.41692</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>202218.87014</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>206975.0654</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>235578.53858</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>303339.46095</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>356814.39674</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>374855.13439</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>407994.35689</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>478252.47301</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>537862.71926</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>489053.61632</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>119108.02389</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>125146.52611</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>121450.04542</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>122416.00866</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>124289.05839</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>112669.29529</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>115504.25248</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>131547.85645</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>174547.54951</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>207159.07592</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>217249.25647</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>234465.03948</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>274145.13524</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>308371.0351</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>293751.9468</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>227772.109671182</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>237366.924976616</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>247726.647313983</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>259588.099334434</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>273162.506765273</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>287944.533978578</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>303214.490316467</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>320489.563175503</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>340228.312234553</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>359268.411014974</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>375676.26822843</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>394358.77688263</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>414661.433611407</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>431763.149905656</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>444746.318180714</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 2</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpO2</t>
